--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/KENTUCKY_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/KENTUCKY_2024.xlsx
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C150">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C231">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C325">
